--- a/数据库信息/基础信息/绩效工资标准字典.xlsx
+++ b/数据库信息/基础信息/绩效工资标准字典.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>岗位</t>
   </si>
@@ -35,6 +35,15 @@
     <t>月绩效工资标准</t>
   </si>
   <si>
+    <t>副科级</t>
+  </si>
+  <si>
+    <t>科员级</t>
+  </si>
+  <si>
+    <t>办事员级</t>
+  </si>
+  <si>
     <t>正高级教师</t>
   </si>
   <si>
@@ -48,12 +57,6 @@
   </si>
   <si>
     <t>三级教师</t>
-  </si>
-  <si>
-    <t>八级管理</t>
-  </si>
-  <si>
-    <t>九级管理</t>
   </si>
   <si>
     <t>技师</t>
@@ -1262,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1282,31 +1285,31 @@
         <v>2</v>
       </c>
       <c r="B2" s="3">
-        <v>1862</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="3" ht="17.5" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>1523</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="4" ht="17.5" spans="1:2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>1309</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="5" ht="17.5" spans="1:2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <v>1241</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="6" ht="17.5" spans="1:2">
@@ -1314,31 +1317,31 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>1128</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="7" ht="17.5" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1241</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="8" ht="17.5" spans="1:2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>1185</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9" ht="17.5" spans="1:2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1331</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="10" ht="17.5" spans="1:2">
@@ -1346,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1219</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="11" ht="17.5" spans="1:2">
@@ -1354,7 +1357,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3">
-        <v>1185</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="12" ht="17.5" spans="1:2">
@@ -1362,7 +1365,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3">
-        <v>1106</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="13" ht="17.5" spans="1:2">
@@ -1373,8 +1376,17 @@
         <v>1106</v>
       </c>
     </row>
+    <row r="14" ht="17.5" spans="1:2">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>